--- a/civic_website/Data/gene_panel.xlsx
+++ b/civic_website/Data/gene_panel.xlsx
@@ -16870,7 +16870,7 @@
         <v>221</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="1" t="s">
         <v>222</v>
       </c>
@@ -16920,7 +16920,7 @@
         <v>225</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="1" t="s">
         <v>226</v>
       </c>
@@ -16970,7 +16970,7 @@
         <v>229</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="1" t="s">
         <v>230</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>233</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="1" t="s">
         <v>234</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>237</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="1" t="s">
         <v>238</v>
       </c>
@@ -17120,7 +17120,7 @@
         <v>241</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="1" t="s">
         <v>242</v>
       </c>
@@ -17170,7 +17170,7 @@
         <v>245</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
       <c r="A58" s="1" t="s">
         <v>246</v>
       </c>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="P58" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="1" t="s">
         <v>249</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>252</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="1" t="s">
         <v>253</v>
       </c>
@@ -17318,7 +17318,7 @@
         <v>256</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="1" t="s">
         <v>257</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>260</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="1" t="s">
         <v>261</v>
       </c>
@@ -17418,7 +17418,7 @@
         <v>264</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
       <c r="A63" s="1" t="s">
         <v>265</v>
       </c>
@@ -17468,7 +17468,7 @@
         <v>268</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="1" t="s">
         <v>269</v>
       </c>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="P64" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="1" t="s">
         <v>274</v>
       </c>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="P65" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="1" t="s">
         <v>277</v>
       </c>
@@ -17614,7 +17614,7 @@
         <v>280</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="1" t="s">
         <v>281</v>
       </c>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="P67" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="1" t="s">
         <v>284</v>
       </c>
